--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260611.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260611.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>7,256,465</t>
+          <t>64,488,708</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>64,488,708</t>
+          <t>7,256,465</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>196,121,191</t>
+          <t>228,753,700</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>228,753,700</t>
+          <t>196,121,191</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>9,678,271</t>
+          <t>235,634,212</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>235,634,212</t>
+          <t>9,678,271</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>202606NYF</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>台灣50ETF股票期貨</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,738</t>
+          <t>20,257,203</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>202606NYF</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>台灣50ETF股票期貨</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>20,257,203</t>
+          <t>1,738</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
